--- a/MCU.xlsx
+++ b/MCU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benja\timeline-site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F362F9D0-2D2E-46B9-82A2-A9D2A1CE2CF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCABDBF1-A4DF-4101-837D-1CE8D2AAF36C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13668" uniqueCount="3977">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13668" uniqueCount="3978">
   <si>
     <t>id</t>
   </si>
@@ -11954,6 +11954,9 @@
   </si>
   <si>
     <t xml:space="preserve">Fox X-Men </t>
+  </si>
+  <si>
+    <t>Special</t>
   </si>
 </sst>
 </file>
@@ -66836,7 +66839,7 @@
         <v>393</v>
       </c>
       <c r="P982" t="s">
-        <v>27</v>
+        <v>3977</v>
       </c>
       <c r="Q982" t="s">
         <v>3328</v>
@@ -70091,7 +70094,7 @@
         <v>393</v>
       </c>
       <c r="P1039" t="s">
-        <v>27</v>
+        <v>3977</v>
       </c>
       <c r="Q1039" t="s">
         <v>3805</v>

--- a/MCU.xlsx
+++ b/MCU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benja\timeline-site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCABDBF1-A4DF-4101-837D-1CE8D2AAF36C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E50E3ED-EA06-42EF-8BFF-73008D8264CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -66786,7 +66786,7 @@
         <v>393</v>
       </c>
       <c r="P981" t="s">
-        <v>27</v>
+        <v>3977</v>
       </c>
       <c r="Q981" t="s">
         <v>3313</v>

--- a/MCU.xlsx
+++ b/MCU.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E50E3ED-EA06-42EF-8BFF-73008D8264CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="21720" windowHeight="12900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MCUDATASHEET" sheetId="1" r:id="rId1"/>
